--- a/exports/performance_run_100000.xlsx
+++ b/exports/performance_run_100000.xlsx
@@ -485,19 +485,19 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>4.674</v>
+        <v>2.475</v>
       </c>
       <c r="E2" t="n">
-        <v>6.054</v>
+        <v>2.658</v>
       </c>
       <c r="F2" t="n">
-        <v>4.562</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>116250</v>
+        <v>116460</v>
       </c>
     </row>
     <row r="3">
@@ -515,19 +515,19 @@
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>4.694</v>
+        <v>4.641</v>
       </c>
       <c r="E3" t="n">
-        <v>4.907</v>
+        <v>5.634</v>
       </c>
       <c r="F3" t="n">
-        <v>4.721</v>
+        <v>4.604</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>115440</v>
+        <v>115800</v>
       </c>
     </row>
     <row r="4">
@@ -545,19 +545,19 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>0.059</v>
+        <v>0.057</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08</v>
+        <v>0.062</v>
       </c>
       <c r="F4" t="n">
-        <v>0.062</v>
+        <v>0.058</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>630</v>
+        <v>660</v>
       </c>
     </row>
     <row r="5">
@@ -575,13 +575,13 @@
         <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>45.233</v>
+        <v>42.939</v>
       </c>
       <c r="E5" t="n">
-        <v>63.159</v>
+        <v>45.616</v>
       </c>
       <c r="F5" t="n">
-        <v>48.217</v>
+        <v>43.437</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -605,19 +605,19 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>9.678000000000001</v>
+        <v>6.986</v>
       </c>
       <c r="E6" t="n">
-        <v>15.45</v>
+        <v>11.218</v>
       </c>
       <c r="F6" t="n">
-        <v>10.456</v>
+        <v>7.62</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>209520</v>
+        <v>209880</v>
       </c>
     </row>
     <row r="7">
@@ -635,19 +635,19 @@
         <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>24.576</v>
+        <v>19.066</v>
       </c>
       <c r="E7" t="n">
-        <v>34.465</v>
+        <v>20.644</v>
       </c>
       <c r="F7" t="n">
-        <v>25.933</v>
+        <v>19.311</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>271470</v>
+        <v>271500</v>
       </c>
     </row>
     <row r="8">
@@ -665,13 +665,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>89.261</v>
+        <v>86.929</v>
       </c>
       <c r="E8" t="n">
-        <v>113.706</v>
+        <v>94.904</v>
       </c>
       <c r="F8" t="n">
-        <v>93.04600000000001</v>
+        <v>88.634</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -695,19 +695,19 @@
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>5.947</v>
+        <v>4.273</v>
       </c>
       <c r="E9" t="n">
-        <v>7.208</v>
+        <v>4.627</v>
       </c>
       <c r="F9" t="n">
-        <v>6.033</v>
+        <v>4.297</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>115980</v>
+        <v>116160</v>
       </c>
     </row>
     <row r="10">
@@ -725,19 +725,19 @@
         <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>3.8</v>
+        <v>1.939</v>
       </c>
       <c r="E10" t="n">
-        <v>4.348</v>
+        <v>2.037</v>
       </c>
       <c r="F10" t="n">
-        <v>3.614</v>
+        <v>1.953</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>116040</v>
+        <v>116220</v>
       </c>
     </row>
     <row r="11">
@@ -755,19 +755,19 @@
         <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>60.59</v>
+        <v>49.877</v>
       </c>
       <c r="E11" t="n">
-        <v>76.58199999999999</v>
+        <v>54.324</v>
       </c>
       <c r="F11" t="n">
-        <v>62.364</v>
+        <v>51.022</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>500340</v>
+        <v>504930</v>
       </c>
     </row>
     <row r="12">
@@ -785,13 +785,13 @@
         <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>68.767</v>
+        <v>46.874</v>
       </c>
       <c r="E12" t="n">
-        <v>76.471</v>
+        <v>48.764</v>
       </c>
       <c r="F12" t="n">
-        <v>68.36199999999999</v>
+        <v>47.055</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -815,13 +815,13 @@
         <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>47.996</v>
+        <v>45.652</v>
       </c>
       <c r="E13" t="n">
-        <v>50.811</v>
+        <v>47.388</v>
       </c>
       <c r="F13" t="n">
-        <v>48.581</v>
+        <v>45.935</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -845,13 +845,13 @@
         <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>41.797</v>
+        <v>40.369</v>
       </c>
       <c r="E14" t="n">
-        <v>43.087</v>
+        <v>41.226</v>
       </c>
       <c r="F14" t="n">
-        <v>41.9</v>
+        <v>40.486</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -875,13 +875,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>109.665</v>
+        <v>104.151</v>
       </c>
       <c r="E15" t="n">
-        <v>126.012</v>
+        <v>111.966</v>
       </c>
       <c r="F15" t="n">
-        <v>111.661</v>
+        <v>105.172</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -905,13 +905,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>134.024</v>
+        <v>69.883</v>
       </c>
       <c r="E16" t="n">
-        <v>203.983</v>
+        <v>72.479</v>
       </c>
       <c r="F16" t="n">
-        <v>142.892</v>
+        <v>70.22</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -935,13 +935,13 @@
         <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>62.364</v>
+        <v>61.306</v>
       </c>
       <c r="E17" t="n">
-        <v>67.242</v>
+        <v>65.779</v>
       </c>
       <c r="F17" t="n">
-        <v>62.926</v>
+        <v>61.813</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -965,13 +965,13 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>96.574</v>
+        <v>85.26600000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>203.075</v>
+        <v>86.298</v>
       </c>
       <c r="F18" t="n">
-        <v>111.143</v>
+        <v>85.441</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -995,13 +995,13 @@
         <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>50.593</v>
+        <v>45.022</v>
       </c>
       <c r="E19" t="n">
-        <v>63.945</v>
+        <v>46.126</v>
       </c>
       <c r="F19" t="n">
-        <v>55.91</v>
+        <v>45.186</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1025,13 +1025,13 @@
         <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>54.131</v>
+        <v>46.646</v>
       </c>
       <c r="E20" t="n">
-        <v>87.27200000000001</v>
+        <v>47.168</v>
       </c>
       <c r="F20" t="n">
-        <v>61.094</v>
+        <v>46.521</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>84.129</v>
+        <v>72.401</v>
       </c>
       <c r="E21" t="n">
-        <v>103.712</v>
+        <v>79.294</v>
       </c>
       <c r="F21" t="n">
-        <v>89.503</v>
+        <v>74.07599999999999</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1085,19 +1085,19 @@
         <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>3.235</v>
+        <v>2.087</v>
       </c>
       <c r="E22" t="n">
-        <v>5.39</v>
+        <v>2.351</v>
       </c>
       <c r="F22" t="n">
-        <v>3.439</v>
+        <v>2.121</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>116100</v>
+        <v>116220</v>
       </c>
     </row>
     <row r="23">
@@ -1115,19 +1115,19 @@
         <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>4.67</v>
+        <v>3.622</v>
       </c>
       <c r="E23" t="n">
-        <v>5.827</v>
+        <v>3.862</v>
       </c>
       <c r="F23" t="n">
-        <v>4.829</v>
+        <v>3.454</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>115200</v>
+        <v>115170</v>
       </c>
     </row>
     <row r="24">
@@ -1145,13 +1145,13 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>0.046</v>
+        <v>0.053</v>
       </c>
       <c r="E24" t="n">
-        <v>0.067</v>
+        <v>0.055</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05</v>
+        <v>0.054</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1175,19 +1175,19 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>35.091</v>
+        <v>24.514</v>
       </c>
       <c r="E25" t="n">
-        <v>53.882</v>
+        <v>25.769</v>
       </c>
       <c r="F25" t="n">
-        <v>38.054</v>
+        <v>24.663</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>170760</v>
+        <v>170730</v>
       </c>
     </row>
     <row r="26">
@@ -1205,19 +1205,19 @@
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>5.76</v>
+        <v>3.815</v>
       </c>
       <c r="E26" t="n">
-        <v>7.182</v>
+        <v>4.564</v>
       </c>
       <c r="F26" t="n">
-        <v>5.861</v>
+        <v>4.029</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>128430</v>
+        <v>128880</v>
       </c>
     </row>
     <row r="27">
@@ -1235,19 +1235,19 @@
         <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>13.898</v>
+        <v>12.277</v>
       </c>
       <c r="E27" t="n">
-        <v>17.505</v>
+        <v>13.574</v>
       </c>
       <c r="F27" t="n">
-        <v>14.491</v>
+        <v>12.023</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>145170</v>
+        <v>144570</v>
       </c>
     </row>
     <row r="28">
@@ -1265,19 +1265,19 @@
         <v>30</v>
       </c>
       <c r="D28" t="n">
-        <v>49.75</v>
+        <v>42.585</v>
       </c>
       <c r="E28" t="n">
-        <v>68.139</v>
+        <v>51.97</v>
       </c>
       <c r="F28" t="n">
-        <v>51.28</v>
+        <v>44.361</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>154890</v>
+        <v>154860</v>
       </c>
     </row>
     <row r="29">
@@ -1295,19 +1295,19 @@
         <v>30</v>
       </c>
       <c r="D29" t="n">
-        <v>3.65</v>
+        <v>3.673</v>
       </c>
       <c r="E29" t="n">
-        <v>4.198</v>
+        <v>3.907</v>
       </c>
       <c r="F29" t="n">
-        <v>3.704</v>
+        <v>3.699</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>115740</v>
+        <v>115530</v>
       </c>
     </row>
     <row r="30">
@@ -1325,19 +1325,19 @@
         <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>7.163</v>
+        <v>3.622</v>
       </c>
       <c r="E30" t="n">
-        <v>12.833</v>
+        <v>3.823</v>
       </c>
       <c r="F30" t="n">
-        <v>7.563</v>
+        <v>3.5</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>115740</v>
+        <v>115530</v>
       </c>
     </row>
     <row r="31">
@@ -1355,19 +1355,19 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>17.863</v>
+        <v>32.114</v>
       </c>
       <c r="E31" t="n">
-        <v>19.756</v>
+        <v>35.045</v>
       </c>
       <c r="F31" t="n">
-        <v>17.935</v>
+        <v>32.599</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>156240</v>
+        <v>154860</v>
       </c>
     </row>
     <row r="32">
@@ -1385,19 +1385,19 @@
         <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>18.506</v>
+        <v>15.538</v>
       </c>
       <c r="E32" t="n">
-        <v>20.775</v>
+        <v>16.062</v>
       </c>
       <c r="F32" t="n">
-        <v>18.856</v>
+        <v>15.633</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>154890</v>
+        <v>154860</v>
       </c>
     </row>
     <row r="33">
@@ -1415,19 +1415,19 @@
         <v>30</v>
       </c>
       <c r="D33" t="n">
-        <v>31.525</v>
+        <v>29.33</v>
       </c>
       <c r="E33" t="n">
-        <v>35.405</v>
+        <v>30.621</v>
       </c>
       <c r="F33" t="n">
-        <v>32.189</v>
+        <v>29.559</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>154890</v>
+        <v>154860</v>
       </c>
     </row>
     <row r="34">
@@ -1445,19 +1445,19 @@
         <v>30</v>
       </c>
       <c r="D34" t="n">
-        <v>16.911</v>
+        <v>15.064</v>
       </c>
       <c r="E34" t="n">
-        <v>18.859</v>
+        <v>15.63</v>
       </c>
       <c r="F34" t="n">
-        <v>17.154</v>
+        <v>15.158</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>154890</v>
+        <v>154860</v>
       </c>
     </row>
     <row r="35">
@@ -1475,19 +1475,19 @@
         <v>30</v>
       </c>
       <c r="D35" t="n">
-        <v>75.23</v>
+        <v>63.966</v>
       </c>
       <c r="E35" t="n">
-        <v>99.173</v>
+        <v>65.28100000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>77.748</v>
+        <v>63.684</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>154890</v>
+        <v>154860</v>
       </c>
     </row>
     <row r="36">
@@ -1505,19 +1505,19 @@
         <v>30</v>
       </c>
       <c r="D36" t="n">
-        <v>19.918</v>
+        <v>17.594</v>
       </c>
       <c r="E36" t="n">
-        <v>25.549</v>
+        <v>19.862</v>
       </c>
       <c r="F36" t="n">
-        <v>20.858</v>
+        <v>17.889</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>154890</v>
+        <v>154860</v>
       </c>
     </row>
     <row r="37">
@@ -1535,19 +1535,19 @@
         <v>30</v>
       </c>
       <c r="D37" t="n">
-        <v>41.163</v>
+        <v>35.755</v>
       </c>
       <c r="E37" t="n">
-        <v>43.685</v>
+        <v>39.664</v>
       </c>
       <c r="F37" t="n">
-        <v>40.6</v>
+        <v>35.729</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>154890</v>
+        <v>154860</v>
       </c>
     </row>
     <row r="38">
@@ -1565,19 +1565,19 @@
         <v>30</v>
       </c>
       <c r="D38" t="n">
-        <v>44.482</v>
+        <v>45.938</v>
       </c>
       <c r="E38" t="n">
-        <v>51.619</v>
+        <v>57.087</v>
       </c>
       <c r="F38" t="n">
-        <v>45.154</v>
+        <v>47.711</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>154890</v>
+        <v>154860</v>
       </c>
     </row>
     <row r="39">
@@ -1595,19 +1595,19 @@
         <v>30</v>
       </c>
       <c r="D39" t="n">
-        <v>30.674</v>
+        <v>26.438</v>
       </c>
       <c r="E39" t="n">
-        <v>34.507</v>
+        <v>27.756</v>
       </c>
       <c r="F39" t="n">
-        <v>31.195</v>
+        <v>26.717</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>154890</v>
+        <v>154860</v>
       </c>
     </row>
     <row r="40">
@@ -1625,19 +1625,19 @@
         <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>38.355</v>
+        <v>31.845</v>
       </c>
       <c r="E40" t="n">
-        <v>64.318</v>
+        <v>32.816</v>
       </c>
       <c r="F40" t="n">
-        <v>43.322</v>
+        <v>31.468</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>154890</v>
+        <v>154860</v>
       </c>
     </row>
     <row r="41">
@@ -1655,19 +1655,19 @@
         <v>30</v>
       </c>
       <c r="D41" t="n">
-        <v>41.655</v>
+        <v>32.749</v>
       </c>
       <c r="E41" t="n">
-        <v>52.626</v>
+        <v>33.746</v>
       </c>
       <c r="F41" t="n">
-        <v>42.528</v>
+        <v>32.547</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>154890</v>
+        <v>154860</v>
       </c>
     </row>
   </sheetData>

--- a/exports/performance_run_100000.xlsx
+++ b/exports/performance_run_100000.xlsx
@@ -485,19 +485,19 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>2.475</v>
+        <v>2.548</v>
       </c>
       <c r="E2" t="n">
-        <v>2.658</v>
+        <v>2.733</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>116460</v>
+        <v>116550</v>
       </c>
     </row>
     <row r="3">
@@ -515,19 +515,19 @@
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>4.641</v>
+        <v>5.863</v>
       </c>
       <c r="E3" t="n">
-        <v>5.634</v>
+        <v>7.067</v>
       </c>
       <c r="F3" t="n">
-        <v>4.604</v>
+        <v>5.786</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>115800</v>
+        <v>115470</v>
       </c>
     </row>
     <row r="4">
@@ -545,13 +545,13 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.057</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.058</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -575,19 +575,19 @@
         <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>42.939</v>
+        <v>34.82</v>
       </c>
       <c r="E5" t="n">
-        <v>45.616</v>
+        <v>36.53</v>
       </c>
       <c r="F5" t="n">
-        <v>43.437</v>
+        <v>34.98</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>515160</v>
+        <v>500850</v>
       </c>
     </row>
     <row r="6">
@@ -605,19 +605,19 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>6.986</v>
+        <v>6.021</v>
       </c>
       <c r="E6" t="n">
-        <v>11.218</v>
+        <v>6.567</v>
       </c>
       <c r="F6" t="n">
-        <v>7.62</v>
+        <v>6.114</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>209880</v>
+        <v>208950</v>
       </c>
     </row>
     <row r="7">
@@ -635,19 +635,19 @@
         <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>19.066</v>
+        <v>18.42</v>
       </c>
       <c r="E7" t="n">
-        <v>20.644</v>
+        <v>20.333</v>
       </c>
       <c r="F7" t="n">
-        <v>19.311</v>
+        <v>18.689</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>271500</v>
+        <v>270660</v>
       </c>
     </row>
     <row r="8">
@@ -665,13 +665,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>86.929</v>
+        <v>85.735</v>
       </c>
       <c r="E8" t="n">
-        <v>94.904</v>
+        <v>89.767</v>
       </c>
       <c r="F8" t="n">
-        <v>88.634</v>
+        <v>86.395</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -695,13 +695,13 @@
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>4.273</v>
+        <v>3.834</v>
       </c>
       <c r="E9" t="n">
-        <v>4.627</v>
+        <v>4.07</v>
       </c>
       <c r="F9" t="n">
-        <v>4.297</v>
+        <v>3.718</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -725,13 +725,13 @@
         <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>1.939</v>
+        <v>1.949</v>
       </c>
       <c r="E10" t="n">
-        <v>2.037</v>
+        <v>2.062</v>
       </c>
       <c r="F10" t="n">
-        <v>1.953</v>
+        <v>1.962</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -755,19 +755,19 @@
         <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>49.877</v>
+        <v>52.141</v>
       </c>
       <c r="E11" t="n">
-        <v>54.324</v>
+        <v>54.595</v>
       </c>
       <c r="F11" t="n">
-        <v>51.022</v>
+        <v>52.406</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>504930</v>
+        <v>504600</v>
       </c>
     </row>
     <row r="12">
@@ -785,13 +785,13 @@
         <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>46.874</v>
+        <v>47.409</v>
       </c>
       <c r="E12" t="n">
-        <v>48.764</v>
+        <v>48.815</v>
       </c>
       <c r="F12" t="n">
-        <v>47.055</v>
+        <v>47.545</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -815,13 +815,13 @@
         <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>45.652</v>
+        <v>46.122</v>
       </c>
       <c r="E13" t="n">
-        <v>47.388</v>
+        <v>47.418</v>
       </c>
       <c r="F13" t="n">
-        <v>45.935</v>
+        <v>46.2</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -845,13 +845,13 @@
         <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>40.369</v>
+        <v>39.112</v>
       </c>
       <c r="E14" t="n">
-        <v>41.226</v>
+        <v>41.062</v>
       </c>
       <c r="F14" t="n">
-        <v>40.486</v>
+        <v>39.495</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -875,13 +875,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>104.151</v>
+        <v>103.157</v>
       </c>
       <c r="E15" t="n">
-        <v>111.966</v>
+        <v>108.687</v>
       </c>
       <c r="F15" t="n">
-        <v>105.172</v>
+        <v>103.956</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -905,13 +905,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>69.883</v>
+        <v>69.333</v>
       </c>
       <c r="E16" t="n">
-        <v>72.479</v>
+        <v>71.688</v>
       </c>
       <c r="F16" t="n">
-        <v>70.22</v>
+        <v>69.386</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -935,13 +935,13 @@
         <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>61.306</v>
+        <v>58.043</v>
       </c>
       <c r="E17" t="n">
-        <v>65.779</v>
+        <v>65.129</v>
       </c>
       <c r="F17" t="n">
-        <v>61.813</v>
+        <v>59.027</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -965,13 +965,13 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>85.26600000000001</v>
+        <v>84.05800000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>86.298</v>
+        <v>91.06399999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>85.441</v>
+        <v>85.139</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -995,13 +995,13 @@
         <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>45.022</v>
+        <v>44.992</v>
       </c>
       <c r="E19" t="n">
-        <v>46.126</v>
+        <v>48.303</v>
       </c>
       <c r="F19" t="n">
-        <v>45.186</v>
+        <v>45.405</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1025,13 +1025,13 @@
         <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>46.646</v>
+        <v>46.289</v>
       </c>
       <c r="E20" t="n">
-        <v>47.168</v>
+        <v>47.879</v>
       </c>
       <c r="F20" t="n">
-        <v>46.521</v>
+        <v>46.36</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>72.401</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>79.294</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>74.07599999999999</v>
+        <v>71.553</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1085,19 +1085,19 @@
         <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>2.087</v>
+        <v>1.082</v>
       </c>
       <c r="E22" t="n">
-        <v>2.351</v>
+        <v>1.169</v>
       </c>
       <c r="F22" t="n">
-        <v>2.121</v>
+        <v>1.091</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>116220</v>
+        <v>35130</v>
       </c>
     </row>
     <row r="23">
@@ -1115,19 +1115,19 @@
         <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>3.622</v>
+        <v>1.284</v>
       </c>
       <c r="E23" t="n">
-        <v>3.862</v>
+        <v>1.433</v>
       </c>
       <c r="F23" t="n">
-        <v>3.454</v>
+        <v>1.287</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>115170</v>
+        <v>35190</v>
       </c>
     </row>
     <row r="24">
@@ -1145,10 +1145,10 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="E24" t="n">
-        <v>0.055</v>
+        <v>0.073</v>
       </c>
       <c r="F24" t="n">
         <v>0.054</v>
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>330</v>
+        <v>360</v>
       </c>
     </row>
     <row r="25">
@@ -1175,19 +1175,19 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>24.514</v>
+        <v>62.202</v>
       </c>
       <c r="E25" t="n">
-        <v>25.769</v>
+        <v>64.072</v>
       </c>
       <c r="F25" t="n">
-        <v>24.663</v>
+        <v>62.466</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>170730</v>
+        <v>287880</v>
       </c>
     </row>
     <row r="26">
@@ -1205,19 +1205,19 @@
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>3.815</v>
+        <v>1.92</v>
       </c>
       <c r="E26" t="n">
-        <v>4.564</v>
+        <v>2.202</v>
       </c>
       <c r="F26" t="n">
-        <v>4.029</v>
+        <v>1.919</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>128880</v>
+        <v>77790</v>
       </c>
     </row>
     <row r="27">
@@ -1235,19 +1235,19 @@
         <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>12.277</v>
+        <v>7.253</v>
       </c>
       <c r="E27" t="n">
-        <v>13.574</v>
+        <v>9.426</v>
       </c>
       <c r="F27" t="n">
-        <v>12.023</v>
+        <v>7.82</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>144570</v>
+        <v>142920</v>
       </c>
     </row>
     <row r="28">
@@ -1265,19 +1265,19 @@
         <v>30</v>
       </c>
       <c r="D28" t="n">
-        <v>42.585</v>
+        <v>40.418</v>
       </c>
       <c r="E28" t="n">
-        <v>51.97</v>
+        <v>42.322</v>
       </c>
       <c r="F28" t="n">
-        <v>44.361</v>
+        <v>40.847</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>154860</v>
+        <v>154890</v>
       </c>
     </row>
     <row r="29">
@@ -1295,19 +1295,19 @@
         <v>30</v>
       </c>
       <c r="D29" t="n">
-        <v>3.673</v>
+        <v>1.038</v>
       </c>
       <c r="E29" t="n">
-        <v>3.907</v>
+        <v>1.099</v>
       </c>
       <c r="F29" t="n">
-        <v>3.699</v>
+        <v>1.044</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>115530</v>
+        <v>35190</v>
       </c>
     </row>
     <row r="30">
@@ -1325,19 +1325,19 @@
         <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>3.622</v>
+        <v>1.04</v>
       </c>
       <c r="E30" t="n">
-        <v>3.823</v>
+        <v>1.104</v>
       </c>
       <c r="F30" t="n">
-        <v>3.5</v>
+        <v>1.035</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>115530</v>
+        <v>35190</v>
       </c>
     </row>
     <row r="31">
@@ -1355,19 +1355,19 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>32.114</v>
+        <v>22.853</v>
       </c>
       <c r="E31" t="n">
-        <v>35.045</v>
+        <v>25.418</v>
       </c>
       <c r="F31" t="n">
-        <v>32.599</v>
+        <v>23.252</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>154860</v>
+        <v>911760</v>
       </c>
     </row>
     <row r="32">
@@ -1385,19 +1385,19 @@
         <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>15.538</v>
+        <v>16.797</v>
       </c>
       <c r="E32" t="n">
-        <v>16.062</v>
+        <v>17.838</v>
       </c>
       <c r="F32" t="n">
-        <v>15.633</v>
+        <v>16.837</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>154860</v>
+        <v>154890</v>
       </c>
     </row>
     <row r="33">
@@ -1415,19 +1415,19 @@
         <v>30</v>
       </c>
       <c r="D33" t="n">
-        <v>29.33</v>
+        <v>27.358</v>
       </c>
       <c r="E33" t="n">
-        <v>30.621</v>
+        <v>29.114</v>
       </c>
       <c r="F33" t="n">
-        <v>29.559</v>
+        <v>27.821</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>154860</v>
+        <v>154890</v>
       </c>
     </row>
     <row r="34">
@@ -1445,19 +1445,19 @@
         <v>30</v>
       </c>
       <c r="D34" t="n">
-        <v>15.064</v>
+        <v>15.059</v>
       </c>
       <c r="E34" t="n">
-        <v>15.63</v>
+        <v>19.647</v>
       </c>
       <c r="F34" t="n">
-        <v>15.158</v>
+        <v>16.19</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>154860</v>
+        <v>154890</v>
       </c>
     </row>
     <row r="35">
@@ -1475,19 +1475,19 @@
         <v>30</v>
       </c>
       <c r="D35" t="n">
-        <v>63.966</v>
+        <v>63.654</v>
       </c>
       <c r="E35" t="n">
-        <v>65.28100000000001</v>
+        <v>75.10599999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>63.684</v>
+        <v>65.589</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>154860</v>
+        <v>154890</v>
       </c>
     </row>
     <row r="36">
@@ -1505,19 +1505,19 @@
         <v>30</v>
       </c>
       <c r="D36" t="n">
-        <v>17.594</v>
+        <v>21.231</v>
       </c>
       <c r="E36" t="n">
-        <v>19.862</v>
+        <v>21.75</v>
       </c>
       <c r="F36" t="n">
-        <v>17.889</v>
+        <v>21.029</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>154860</v>
+        <v>154890</v>
       </c>
     </row>
     <row r="37">
@@ -1535,19 +1535,19 @@
         <v>30</v>
       </c>
       <c r="D37" t="n">
-        <v>35.755</v>
+        <v>30.763</v>
       </c>
       <c r="E37" t="n">
-        <v>39.664</v>
+        <v>31.482</v>
       </c>
       <c r="F37" t="n">
-        <v>35.729</v>
+        <v>30.831</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>154860</v>
+        <v>154890</v>
       </c>
     </row>
     <row r="38">
@@ -1565,19 +1565,19 @@
         <v>30</v>
       </c>
       <c r="D38" t="n">
-        <v>45.938</v>
+        <v>41.804</v>
       </c>
       <c r="E38" t="n">
-        <v>57.087</v>
+        <v>46.799</v>
       </c>
       <c r="F38" t="n">
-        <v>47.711</v>
+        <v>42.395</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>154860</v>
+        <v>154890</v>
       </c>
     </row>
     <row r="39">
@@ -1595,19 +1595,19 @@
         <v>30</v>
       </c>
       <c r="D39" t="n">
-        <v>26.438</v>
+        <v>24.635</v>
       </c>
       <c r="E39" t="n">
-        <v>27.756</v>
+        <v>25.491</v>
       </c>
       <c r="F39" t="n">
-        <v>26.717</v>
+        <v>24.57</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>154860</v>
+        <v>154890</v>
       </c>
     </row>
     <row r="40">
@@ -1625,19 +1625,19 @@
         <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>31.845</v>
+        <v>28.592</v>
       </c>
       <c r="E40" t="n">
-        <v>32.816</v>
+        <v>31.696</v>
       </c>
       <c r="F40" t="n">
-        <v>31.468</v>
+        <v>28.304</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>154860</v>
+        <v>154890</v>
       </c>
     </row>
     <row r="41">
@@ -1655,19 +1655,19 @@
         <v>30</v>
       </c>
       <c r="D41" t="n">
-        <v>32.749</v>
+        <v>26.204</v>
       </c>
       <c r="E41" t="n">
-        <v>33.746</v>
+        <v>31.518</v>
       </c>
       <c r="F41" t="n">
-        <v>32.547</v>
+        <v>27.049</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>154860</v>
+        <v>154890</v>
       </c>
     </row>
   </sheetData>

--- a/exports/performance_run_100000.xlsx
+++ b/exports/performance_run_100000.xlsx
@@ -485,13 +485,13 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>2.548</v>
+        <v>7.002</v>
       </c>
       <c r="E2" t="n">
-        <v>2.733</v>
+        <v>8.082000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.57</v>
+        <v>7.134</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -515,19 +515,19 @@
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>5.863</v>
+        <v>14.553</v>
       </c>
       <c r="E3" t="n">
-        <v>7.067</v>
+        <v>25.735</v>
       </c>
       <c r="F3" t="n">
-        <v>5.786</v>
+        <v>16.525</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>115470</v>
+        <v>115620</v>
       </c>
     </row>
     <row r="4">
@@ -545,13 +545,13 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>0.056</v>
+        <v>0.11</v>
       </c>
       <c r="E4" t="n">
-        <v>0.065</v>
+        <v>0.176</v>
       </c>
       <c r="F4" t="n">
-        <v>0.057</v>
+        <v>0.121</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -575,19 +575,19 @@
         <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>34.82</v>
+        <v>66.883</v>
       </c>
       <c r="E5" t="n">
-        <v>36.53</v>
+        <v>70.786</v>
       </c>
       <c r="F5" t="n">
-        <v>34.98</v>
+        <v>67.074</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>500850</v>
+        <v>502740</v>
       </c>
     </row>
     <row r="6">
@@ -605,19 +605,19 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>6.021</v>
+        <v>13.34</v>
       </c>
       <c r="E6" t="n">
-        <v>6.567</v>
+        <v>13.921</v>
       </c>
       <c r="F6" t="n">
-        <v>6.114</v>
+        <v>13.351</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>208950</v>
+        <v>211890</v>
       </c>
     </row>
     <row r="7">
@@ -635,19 +635,19 @@
         <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>18.42</v>
+        <v>34.523</v>
       </c>
       <c r="E7" t="n">
-        <v>20.333</v>
+        <v>43.076</v>
       </c>
       <c r="F7" t="n">
-        <v>18.689</v>
+        <v>36.014</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>270660</v>
+        <v>271350</v>
       </c>
     </row>
     <row r="8">
@@ -665,13 +665,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>85.735</v>
+        <v>157.485</v>
       </c>
       <c r="E8" t="n">
-        <v>89.767</v>
+        <v>193.283</v>
       </c>
       <c r="F8" t="n">
-        <v>86.395</v>
+        <v>162.676</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -695,19 +695,19 @@
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>3.834</v>
+        <v>8.192</v>
       </c>
       <c r="E9" t="n">
-        <v>4.07</v>
+        <v>8.573</v>
       </c>
       <c r="F9" t="n">
-        <v>3.718</v>
+        <v>8.196999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>116160</v>
+        <v>117000</v>
       </c>
     </row>
     <row r="10">
@@ -725,13 +725,13 @@
         <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>1.949</v>
+        <v>3.971</v>
       </c>
       <c r="E10" t="n">
-        <v>2.062</v>
+        <v>4.483</v>
       </c>
       <c r="F10" t="n">
-        <v>1.962</v>
+        <v>4.033</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -755,19 +755,19 @@
         <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>52.141</v>
+        <v>93.167</v>
       </c>
       <c r="E11" t="n">
-        <v>54.595</v>
+        <v>97.908</v>
       </c>
       <c r="F11" t="n">
-        <v>52.406</v>
+        <v>93.89700000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>504600</v>
+        <v>515820</v>
       </c>
     </row>
     <row r="12">
@@ -785,19 +785,19 @@
         <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>47.409</v>
+        <v>76.901</v>
       </c>
       <c r="E12" t="n">
-        <v>48.815</v>
+        <v>80.373</v>
       </c>
       <c r="F12" t="n">
-        <v>47.545</v>
+        <v>77.264</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>498990</v>
+        <v>997980</v>
       </c>
     </row>
     <row r="13">
@@ -815,13 +815,13 @@
         <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>46.122</v>
+        <v>72.39100000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>47.418</v>
+        <v>80.76300000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>46.2</v>
+        <v>74.504</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -845,13 +845,13 @@
         <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>39.112</v>
+        <v>59.636</v>
       </c>
       <c r="E14" t="n">
-        <v>41.062</v>
+        <v>63.151</v>
       </c>
       <c r="F14" t="n">
-        <v>39.495</v>
+        <v>60.103</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -875,13 +875,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>103.157</v>
+        <v>190.434</v>
       </c>
       <c r="E15" t="n">
-        <v>108.687</v>
+        <v>213.83</v>
       </c>
       <c r="F15" t="n">
-        <v>103.956</v>
+        <v>196.52</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -905,13 +905,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>69.333</v>
+        <v>126.582</v>
       </c>
       <c r="E16" t="n">
-        <v>71.688</v>
+        <v>141.533</v>
       </c>
       <c r="F16" t="n">
-        <v>69.386</v>
+        <v>129.868</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -935,13 +935,13 @@
         <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>58.043</v>
+        <v>99.099</v>
       </c>
       <c r="E17" t="n">
-        <v>65.129</v>
+        <v>114.075</v>
       </c>
       <c r="F17" t="n">
-        <v>59.027</v>
+        <v>101.519</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -965,13 +965,13 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>84.05800000000001</v>
+        <v>149.384</v>
       </c>
       <c r="E18" t="n">
-        <v>91.06399999999999</v>
+        <v>170.811</v>
       </c>
       <c r="F18" t="n">
-        <v>85.139</v>
+        <v>153.754</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -995,13 +995,13 @@
         <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>44.992</v>
+        <v>70.387</v>
       </c>
       <c r="E19" t="n">
-        <v>48.303</v>
+        <v>83.14100000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>45.405</v>
+        <v>72.376</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1025,13 +1025,13 @@
         <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>46.289</v>
+        <v>72.363</v>
       </c>
       <c r="E20" t="n">
-        <v>47.879</v>
+        <v>78.21299999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>46.36</v>
+        <v>73.625</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>71.26000000000001</v>
+        <v>129.981</v>
       </c>
       <c r="E21" t="n">
-        <v>73.79000000000001</v>
+        <v>135.103</v>
       </c>
       <c r="F21" t="n">
-        <v>71.553</v>
+        <v>130.562</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1085,19 +1085,19 @@
         <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>1.082</v>
+        <v>1.285</v>
       </c>
       <c r="E22" t="n">
-        <v>1.169</v>
+        <v>1.427</v>
       </c>
       <c r="F22" t="n">
-        <v>1.091</v>
+        <v>1.313</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>35130</v>
+        <v>870</v>
       </c>
     </row>
     <row r="23">
@@ -1115,19 +1115,19 @@
         <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>1.284</v>
+        <v>1.676</v>
       </c>
       <c r="E23" t="n">
-        <v>1.433</v>
+        <v>1.726</v>
       </c>
       <c r="F23" t="n">
-        <v>1.287</v>
+        <v>1.675</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>35190</v>
+        <v>870</v>
       </c>
     </row>
     <row r="24">
@@ -1145,19 +1145,19 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>0.052</v>
+        <v>0.067</v>
       </c>
       <c r="E24" t="n">
-        <v>0.073</v>
+        <v>0.09</v>
       </c>
       <c r="F24" t="n">
-        <v>0.054</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>360</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25">
@@ -1175,19 +1175,19 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>62.202</v>
+        <v>135.382</v>
       </c>
       <c r="E25" t="n">
-        <v>64.072</v>
+        <v>143.896</v>
       </c>
       <c r="F25" t="n">
-        <v>62.466</v>
+        <v>138.07</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>287880</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="26">
@@ -1205,19 +1205,19 @@
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>1.92</v>
+        <v>2.429</v>
       </c>
       <c r="E26" t="n">
-        <v>2.202</v>
+        <v>2.524</v>
       </c>
       <c r="F26" t="n">
-        <v>1.919</v>
+        <v>2.44</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>77790</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="27">
@@ -1235,19 +1235,19 @@
         <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>7.253</v>
+        <v>17.296</v>
       </c>
       <c r="E27" t="n">
-        <v>9.426</v>
+        <v>21.317</v>
       </c>
       <c r="F27" t="n">
-        <v>7.82</v>
+        <v>17.663</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>142920</v>
+        <v>144120</v>
       </c>
     </row>
     <row r="28">
@@ -1265,19 +1265,19 @@
         <v>30</v>
       </c>
       <c r="D28" t="n">
-        <v>40.418</v>
+        <v>89.56699999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>42.322</v>
+        <v>97.354</v>
       </c>
       <c r="F28" t="n">
-        <v>40.847</v>
+        <v>91.255</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>154890</v>
+        <v>154920</v>
       </c>
     </row>
     <row r="29">
@@ -1295,19 +1295,19 @@
         <v>30</v>
       </c>
       <c r="D29" t="n">
-        <v>1.038</v>
+        <v>1.196</v>
       </c>
       <c r="E29" t="n">
-        <v>1.099</v>
+        <v>1.279</v>
       </c>
       <c r="F29" t="n">
-        <v>1.044</v>
+        <v>1.211</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>35190</v>
+        <v>870</v>
       </c>
     </row>
     <row r="30">
@@ -1325,19 +1325,19 @@
         <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>1.04</v>
+        <v>1.211</v>
       </c>
       <c r="E30" t="n">
-        <v>1.104</v>
+        <v>1.275</v>
       </c>
       <c r="F30" t="n">
-        <v>1.035</v>
+        <v>1.222</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>35190</v>
+        <v>870</v>
       </c>
     </row>
     <row r="31">
@@ -1355,19 +1355,19 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>22.853</v>
+        <v>35.451</v>
       </c>
       <c r="E31" t="n">
-        <v>25.418</v>
+        <v>44.533</v>
       </c>
       <c r="F31" t="n">
-        <v>23.252</v>
+        <v>37.005</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>911760</v>
+        <v>17970</v>
       </c>
     </row>
     <row r="32">
@@ -1385,19 +1385,19 @@
         <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>16.797</v>
+        <v>28.663</v>
       </c>
       <c r="E32" t="n">
-        <v>17.838</v>
+        <v>30.945</v>
       </c>
       <c r="F32" t="n">
-        <v>16.837</v>
+        <v>29.008</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>154890</v>
+        <v>309840</v>
       </c>
     </row>
     <row r="33">
@@ -1415,19 +1415,19 @@
         <v>30</v>
       </c>
       <c r="D33" t="n">
-        <v>27.358</v>
+        <v>50.328</v>
       </c>
       <c r="E33" t="n">
-        <v>29.114</v>
+        <v>55.712</v>
       </c>
       <c r="F33" t="n">
-        <v>27.821</v>
+        <v>51.416</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>154890</v>
+        <v>154920</v>
       </c>
     </row>
     <row r="34">
@@ -1445,19 +1445,19 @@
         <v>30</v>
       </c>
       <c r="D34" t="n">
-        <v>15.059</v>
+        <v>25.773</v>
       </c>
       <c r="E34" t="n">
-        <v>19.647</v>
+        <v>28.216</v>
       </c>
       <c r="F34" t="n">
-        <v>16.19</v>
+        <v>26.235</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>154890</v>
+        <v>154920</v>
       </c>
     </row>
     <row r="35">
@@ -1475,19 +1475,19 @@
         <v>30</v>
       </c>
       <c r="D35" t="n">
-        <v>63.654</v>
+        <v>143.536</v>
       </c>
       <c r="E35" t="n">
-        <v>75.10599999999999</v>
+        <v>151.791</v>
       </c>
       <c r="F35" t="n">
-        <v>65.589</v>
+        <v>144.345</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>154890</v>
+        <v>154920</v>
       </c>
     </row>
     <row r="36">
@@ -1505,19 +1505,19 @@
         <v>30</v>
       </c>
       <c r="D36" t="n">
-        <v>21.231</v>
+        <v>28.562</v>
       </c>
       <c r="E36" t="n">
-        <v>21.75</v>
+        <v>33.575</v>
       </c>
       <c r="F36" t="n">
-        <v>21.029</v>
+        <v>29.285</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>154890</v>
+        <v>154920</v>
       </c>
     </row>
     <row r="37">
@@ -1535,19 +1535,19 @@
         <v>30</v>
       </c>
       <c r="D37" t="n">
-        <v>30.763</v>
+        <v>68.437</v>
       </c>
       <c r="E37" t="n">
-        <v>31.482</v>
+        <v>74.996</v>
       </c>
       <c r="F37" t="n">
-        <v>30.831</v>
+        <v>69.642</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>154890</v>
+        <v>154920</v>
       </c>
     </row>
     <row r="38">
@@ -1565,19 +1565,19 @@
         <v>30</v>
       </c>
       <c r="D38" t="n">
-        <v>41.804</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>46.799</v>
+        <v>100.68</v>
       </c>
       <c r="F38" t="n">
-        <v>42.395</v>
+        <v>94.232</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>154890</v>
+        <v>154920</v>
       </c>
     </row>
     <row r="39">
@@ -1595,19 +1595,19 @@
         <v>30</v>
       </c>
       <c r="D39" t="n">
-        <v>24.635</v>
+        <v>44.91</v>
       </c>
       <c r="E39" t="n">
-        <v>25.491</v>
+        <v>47.476</v>
       </c>
       <c r="F39" t="n">
-        <v>24.57</v>
+        <v>45.255</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>154890</v>
+        <v>154920</v>
       </c>
     </row>
     <row r="40">
@@ -1625,19 +1625,19 @@
         <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>28.592</v>
+        <v>52.357</v>
       </c>
       <c r="E40" t="n">
-        <v>31.696</v>
+        <v>61.949</v>
       </c>
       <c r="F40" t="n">
-        <v>28.304</v>
+        <v>57.006</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>154890</v>
+        <v>154920</v>
       </c>
     </row>
     <row r="41">
@@ -1655,19 +1655,19 @@
         <v>30</v>
       </c>
       <c r="D41" t="n">
-        <v>26.204</v>
+        <v>57.835</v>
       </c>
       <c r="E41" t="n">
-        <v>31.518</v>
+        <v>59.862</v>
       </c>
       <c r="F41" t="n">
-        <v>27.049</v>
+        <v>58.162</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>154890</v>
+        <v>154920</v>
       </c>
     </row>
   </sheetData>

--- a/exports/performance_run_100000.xlsx
+++ b/exports/performance_run_100000.xlsx
@@ -485,19 +485,19 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>7.002</v>
+        <v>2.763</v>
       </c>
       <c r="E2" t="n">
-        <v>8.082000000000001</v>
+        <v>3.703</v>
       </c>
       <c r="F2" t="n">
-        <v>7.134</v>
+        <v>2.829</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>116550</v>
+        <v>116490</v>
       </c>
     </row>
     <row r="3">
@@ -515,13 +515,13 @@
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>14.553</v>
+        <v>6.756</v>
       </c>
       <c r="E3" t="n">
-        <v>25.735</v>
+        <v>8.956</v>
       </c>
       <c r="F3" t="n">
-        <v>16.525</v>
+        <v>7.117</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -545,13 +545,13 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>0.11</v>
+        <v>0.059</v>
       </c>
       <c r="E4" t="n">
-        <v>0.176</v>
+        <v>0.102</v>
       </c>
       <c r="F4" t="n">
-        <v>0.121</v>
+        <v>0.064</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -575,13 +575,13 @@
         <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>66.883</v>
+        <v>38.907</v>
       </c>
       <c r="E5" t="n">
-        <v>70.786</v>
+        <v>40.56</v>
       </c>
       <c r="F5" t="n">
-        <v>67.074</v>
+        <v>39.009</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -605,19 +605,19 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>13.34</v>
+        <v>6.925</v>
       </c>
       <c r="E6" t="n">
-        <v>13.921</v>
+        <v>8.925000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>13.351</v>
+        <v>7.379</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>211890</v>
+        <v>214890</v>
       </c>
     </row>
     <row r="7">
@@ -635,13 +635,13 @@
         <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>34.523</v>
+        <v>20.563</v>
       </c>
       <c r="E7" t="n">
-        <v>43.076</v>
+        <v>23.295</v>
       </c>
       <c r="F7" t="n">
-        <v>36.014</v>
+        <v>21.046</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -665,13 +665,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>157.485</v>
+        <v>89.265</v>
       </c>
       <c r="E8" t="n">
-        <v>193.283</v>
+        <v>93.57299999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>162.676</v>
+        <v>89.55200000000001</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -695,13 +695,13 @@
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>8.192</v>
+        <v>4.264</v>
       </c>
       <c r="E9" t="n">
-        <v>8.573</v>
+        <v>5.222</v>
       </c>
       <c r="F9" t="n">
-        <v>8.196999999999999</v>
+        <v>4.421</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -725,13 +725,13 @@
         <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>3.971</v>
+        <v>2.025</v>
       </c>
       <c r="E10" t="n">
-        <v>4.483</v>
+        <v>2.196</v>
       </c>
       <c r="F10" t="n">
-        <v>4.033</v>
+        <v>2.037</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -755,13 +755,13 @@
         <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>93.167</v>
+        <v>55.261</v>
       </c>
       <c r="E11" t="n">
-        <v>97.908</v>
+        <v>57.738</v>
       </c>
       <c r="F11" t="n">
-        <v>93.89700000000001</v>
+        <v>55.515</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -785,13 +785,13 @@
         <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>76.901</v>
+        <v>49.58</v>
       </c>
       <c r="E12" t="n">
-        <v>80.373</v>
+        <v>51.068</v>
       </c>
       <c r="F12" t="n">
-        <v>77.264</v>
+        <v>49.678</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -815,13 +815,13 @@
         <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>72.39100000000001</v>
+        <v>48.018</v>
       </c>
       <c r="E13" t="n">
-        <v>80.76300000000001</v>
+        <v>52.567</v>
       </c>
       <c r="F13" t="n">
-        <v>74.504</v>
+        <v>48.532</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -845,13 +845,13 @@
         <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>59.636</v>
+        <v>40.674</v>
       </c>
       <c r="E14" t="n">
-        <v>63.151</v>
+        <v>44.097</v>
       </c>
       <c r="F14" t="n">
-        <v>60.103</v>
+        <v>41.345</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -875,13 +875,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>190.434</v>
+        <v>105.309</v>
       </c>
       <c r="E15" t="n">
-        <v>213.83</v>
+        <v>109.249</v>
       </c>
       <c r="F15" t="n">
-        <v>196.52</v>
+        <v>105.708</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -905,13 +905,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>126.582</v>
+        <v>72.943</v>
       </c>
       <c r="E16" t="n">
-        <v>141.533</v>
+        <v>78.3</v>
       </c>
       <c r="F16" t="n">
-        <v>129.868</v>
+        <v>73.702</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -935,13 +935,13 @@
         <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>99.099</v>
+        <v>62.061</v>
       </c>
       <c r="E17" t="n">
-        <v>114.075</v>
+        <v>65.331</v>
       </c>
       <c r="F17" t="n">
-        <v>101.519</v>
+        <v>62.32</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -965,13 +965,13 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>149.384</v>
+        <v>85.977</v>
       </c>
       <c r="E18" t="n">
-        <v>170.811</v>
+        <v>88.879</v>
       </c>
       <c r="F18" t="n">
-        <v>153.754</v>
+        <v>86.556</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -995,13 +995,13 @@
         <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>70.387</v>
+        <v>47.141</v>
       </c>
       <c r="E19" t="n">
-        <v>83.14100000000001</v>
+        <v>49.172</v>
       </c>
       <c r="F19" t="n">
-        <v>72.376</v>
+        <v>47.347</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1025,13 +1025,13 @@
         <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>72.363</v>
+        <v>49.18</v>
       </c>
       <c r="E20" t="n">
-        <v>78.21299999999999</v>
+        <v>51.446</v>
       </c>
       <c r="F20" t="n">
-        <v>73.625</v>
+        <v>49.406</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>129.981</v>
+        <v>74.627</v>
       </c>
       <c r="E21" t="n">
-        <v>135.103</v>
+        <v>77.63500000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>130.562</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1085,13 +1085,13 @@
         <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>1.285</v>
+        <v>0.721</v>
       </c>
       <c r="E22" t="n">
-        <v>1.427</v>
+        <v>0.801</v>
       </c>
       <c r="F22" t="n">
-        <v>1.313</v>
+        <v>0.73</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1115,13 +1115,13 @@
         <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>1.676</v>
+        <v>0.92</v>
       </c>
       <c r="E23" t="n">
-        <v>1.726</v>
+        <v>1.029</v>
       </c>
       <c r="F23" t="n">
-        <v>1.675</v>
+        <v>0.918</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1145,13 +1145,13 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>0.067</v>
+        <v>0.043</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09</v>
+        <v>0.051</v>
       </c>
       <c r="F24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.043</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1175,13 +1175,13 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>135.382</v>
+        <v>60.015</v>
       </c>
       <c r="E25" t="n">
-        <v>143.896</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>138.07</v>
+        <v>60.36</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1205,19 +1205,19 @@
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>2.429</v>
+        <v>1.281</v>
       </c>
       <c r="E26" t="n">
-        <v>2.524</v>
+        <v>1.41</v>
       </c>
       <c r="F26" t="n">
-        <v>2.44</v>
+        <v>1.241</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1470</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="27">
@@ -1235,19 +1235,19 @@
         <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>17.296</v>
+        <v>8.894</v>
       </c>
       <c r="E27" t="n">
-        <v>21.317</v>
+        <v>10.178</v>
       </c>
       <c r="F27" t="n">
-        <v>17.663</v>
+        <v>8.871</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>144120</v>
+        <v>144300</v>
       </c>
     </row>
     <row r="28">
@@ -1265,19 +1265,19 @@
         <v>30</v>
       </c>
       <c r="D28" t="n">
-        <v>89.56699999999999</v>
+        <v>43.311</v>
       </c>
       <c r="E28" t="n">
-        <v>97.354</v>
+        <v>53.64</v>
       </c>
       <c r="F28" t="n">
-        <v>91.255</v>
+        <v>45.654</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>154920</v>
+        <v>154890</v>
       </c>
     </row>
     <row r="29">
@@ -1295,13 +1295,13 @@
         <v>30</v>
       </c>
       <c r="D29" t="n">
-        <v>1.196</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>1.279</v>
+        <v>0.783</v>
       </c>
       <c r="F29" t="n">
-        <v>1.211</v>
+        <v>0.705</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1325,13 +1325,13 @@
         <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>1.211</v>
+        <v>0.697</v>
       </c>
       <c r="E30" t="n">
-        <v>1.275</v>
+        <v>0.763</v>
       </c>
       <c r="F30" t="n">
-        <v>1.222</v>
+        <v>0.701</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1355,19 +1355,19 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>35.451</v>
+        <v>15.533</v>
       </c>
       <c r="E31" t="n">
-        <v>44.533</v>
+        <v>16.306</v>
       </c>
       <c r="F31" t="n">
-        <v>37.005</v>
+        <v>15.627</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>17970</v>
+        <v>17610</v>
       </c>
     </row>
     <row r="32">
@@ -1385,19 +1385,19 @@
         <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>28.663</v>
+        <v>18.531</v>
       </c>
       <c r="E32" t="n">
-        <v>30.945</v>
+        <v>19.559</v>
       </c>
       <c r="F32" t="n">
-        <v>29.008</v>
+        <v>18.658</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>309840</v>
+        <v>309780</v>
       </c>
     </row>
     <row r="33">
@@ -1415,19 +1415,19 @@
         <v>30</v>
       </c>
       <c r="D33" t="n">
-        <v>50.328</v>
+        <v>27.686</v>
       </c>
       <c r="E33" t="n">
-        <v>55.712</v>
+        <v>28.372</v>
       </c>
       <c r="F33" t="n">
-        <v>51.416</v>
+        <v>27.771</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>154920</v>
+        <v>154890</v>
       </c>
     </row>
     <row r="34">
@@ -1445,19 +1445,19 @@
         <v>30</v>
       </c>
       <c r="D34" t="n">
-        <v>25.773</v>
+        <v>15.356</v>
       </c>
       <c r="E34" t="n">
-        <v>28.216</v>
+        <v>18.775</v>
       </c>
       <c r="F34" t="n">
-        <v>26.235</v>
+        <v>15.804</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>154920</v>
+        <v>154890</v>
       </c>
     </row>
     <row r="35">
@@ -1475,19 +1475,19 @@
         <v>30</v>
       </c>
       <c r="D35" t="n">
-        <v>143.536</v>
+        <v>73.91200000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>151.791</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>144.345</v>
+        <v>72.637</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>154920</v>
+        <v>154890</v>
       </c>
     </row>
     <row r="36">
@@ -1505,19 +1505,19 @@
         <v>30</v>
       </c>
       <c r="D36" t="n">
-        <v>28.562</v>
+        <v>17.046</v>
       </c>
       <c r="E36" t="n">
-        <v>33.575</v>
+        <v>19.331</v>
       </c>
       <c r="F36" t="n">
-        <v>29.285</v>
+        <v>17.477</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>154920</v>
+        <v>154890</v>
       </c>
     </row>
     <row r="37">
@@ -1535,19 +1535,19 @@
         <v>30</v>
       </c>
       <c r="D37" t="n">
-        <v>68.437</v>
+        <v>37.262</v>
       </c>
       <c r="E37" t="n">
-        <v>74.996</v>
+        <v>38.546</v>
       </c>
       <c r="F37" t="n">
-        <v>69.642</v>
+        <v>35.956</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>154920</v>
+        <v>154890</v>
       </c>
     </row>
     <row r="38">
@@ -1565,19 +1565,19 @@
         <v>30</v>
       </c>
       <c r="D38" t="n">
-        <v>92.70999999999999</v>
+        <v>44.058</v>
       </c>
       <c r="E38" t="n">
-        <v>100.68</v>
+        <v>52.371</v>
       </c>
       <c r="F38" t="n">
-        <v>94.232</v>
+        <v>45.735</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>154920</v>
+        <v>154890</v>
       </c>
     </row>
     <row r="39">
@@ -1595,19 +1595,19 @@
         <v>30</v>
       </c>
       <c r="D39" t="n">
-        <v>44.91</v>
+        <v>25.878</v>
       </c>
       <c r="E39" t="n">
-        <v>47.476</v>
+        <v>27.079</v>
       </c>
       <c r="F39" t="n">
-        <v>45.255</v>
+        <v>26.04</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>154920</v>
+        <v>154890</v>
       </c>
     </row>
     <row r="40">
@@ -1625,19 +1625,19 @@
         <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>52.357</v>
+        <v>29.013</v>
       </c>
       <c r="E40" t="n">
-        <v>61.949</v>
+        <v>30.071</v>
       </c>
       <c r="F40" t="n">
-        <v>57.006</v>
+        <v>29.215</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>154920</v>
+        <v>154890</v>
       </c>
     </row>
     <row r="41">
@@ -1655,19 +1655,19 @@
         <v>30</v>
       </c>
       <c r="D41" t="n">
-        <v>57.835</v>
+        <v>31.494</v>
       </c>
       <c r="E41" t="n">
-        <v>59.862</v>
+        <v>32.575</v>
       </c>
       <c r="F41" t="n">
-        <v>58.162</v>
+        <v>31.654</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>154920</v>
+        <v>154890</v>
       </c>
     </row>
   </sheetData>

--- a/exports/performance_run_100000.xlsx
+++ b/exports/performance_run_100000.xlsx
@@ -485,19 +485,19 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>2.763</v>
+        <v>3.507</v>
       </c>
       <c r="E2" t="n">
-        <v>3.703</v>
+        <v>4.729</v>
       </c>
       <c r="F2" t="n">
-        <v>2.829</v>
+        <v>3.708</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>116490</v>
+        <v>116520</v>
       </c>
     </row>
     <row r="3">
@@ -515,13 +515,13 @@
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>6.756</v>
+        <v>6.693</v>
       </c>
       <c r="E3" t="n">
-        <v>8.956</v>
+        <v>7.697</v>
       </c>
       <c r="F3" t="n">
-        <v>7.117</v>
+        <v>6.852</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -545,13 +545,13 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>0.059</v>
+        <v>0.063</v>
       </c>
       <c r="E4" t="n">
-        <v>0.102</v>
+        <v>0.099</v>
       </c>
       <c r="F4" t="n">
-        <v>0.064</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -575,13 +575,13 @@
         <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>38.907</v>
+        <v>39.682</v>
       </c>
       <c r="E5" t="n">
-        <v>40.56</v>
+        <v>44.601</v>
       </c>
       <c r="F5" t="n">
-        <v>39.009</v>
+        <v>40.251</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -605,19 +605,19 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>6.925</v>
+        <v>8.599</v>
       </c>
       <c r="E6" t="n">
-        <v>8.925000000000001</v>
+        <v>10.559</v>
       </c>
       <c r="F6" t="n">
-        <v>7.379</v>
+        <v>8.683999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>214890</v>
+        <v>212370</v>
       </c>
     </row>
     <row r="7">
@@ -635,13 +635,13 @@
         <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>20.563</v>
+        <v>20.018</v>
       </c>
       <c r="E7" t="n">
-        <v>23.295</v>
+        <v>22.335</v>
       </c>
       <c r="F7" t="n">
-        <v>21.046</v>
+        <v>20.324</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -665,13 +665,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>89.265</v>
+        <v>88.03100000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>93.57299999999999</v>
+        <v>92.842</v>
       </c>
       <c r="F8" t="n">
-        <v>89.55200000000001</v>
+        <v>88.40900000000001</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -695,19 +695,19 @@
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>4.264</v>
+        <v>5.18</v>
       </c>
       <c r="E9" t="n">
-        <v>5.222</v>
+        <v>7.111</v>
       </c>
       <c r="F9" t="n">
-        <v>4.421</v>
+        <v>5.609</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>117000</v>
+        <v>116880</v>
       </c>
     </row>
     <row r="10">
@@ -725,19 +725,19 @@
         <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>2.025</v>
+        <v>3.48</v>
       </c>
       <c r="E10" t="n">
-        <v>2.196</v>
+        <v>4.557</v>
       </c>
       <c r="F10" t="n">
-        <v>2.037</v>
+        <v>3.511</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>116220</v>
+        <v>116160</v>
       </c>
     </row>
     <row r="11">
@@ -755,13 +755,13 @@
         <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>55.261</v>
+        <v>59.436</v>
       </c>
       <c r="E11" t="n">
-        <v>57.738</v>
+        <v>66.952</v>
       </c>
       <c r="F11" t="n">
-        <v>55.515</v>
+        <v>60.215</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -785,13 +785,13 @@
         <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>49.58</v>
+        <v>51.6</v>
       </c>
       <c r="E12" t="n">
-        <v>51.068</v>
+        <v>55.255</v>
       </c>
       <c r="F12" t="n">
-        <v>49.678</v>
+        <v>51.697</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -815,13 +815,13 @@
         <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>48.018</v>
+        <v>47.667</v>
       </c>
       <c r="E13" t="n">
-        <v>52.567</v>
+        <v>50.781</v>
       </c>
       <c r="F13" t="n">
-        <v>48.532</v>
+        <v>49.668</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -845,13 +845,13 @@
         <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>40.674</v>
+        <v>44.686</v>
       </c>
       <c r="E14" t="n">
-        <v>44.097</v>
+        <v>56.795</v>
       </c>
       <c r="F14" t="n">
-        <v>41.345</v>
+        <v>48.138</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -875,13 +875,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>105.309</v>
+        <v>112.568</v>
       </c>
       <c r="E15" t="n">
-        <v>109.249</v>
+        <v>120.371</v>
       </c>
       <c r="F15" t="n">
-        <v>105.708</v>
+        <v>112.991</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -905,13 +905,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>72.943</v>
+        <v>74.798</v>
       </c>
       <c r="E16" t="n">
-        <v>78.3</v>
+        <v>80.878</v>
       </c>
       <c r="F16" t="n">
-        <v>73.702</v>
+        <v>75.505</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -935,13 +935,13 @@
         <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>62.061</v>
+        <v>63.139</v>
       </c>
       <c r="E17" t="n">
-        <v>65.331</v>
+        <v>67.104</v>
       </c>
       <c r="F17" t="n">
-        <v>62.32</v>
+        <v>63.647</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -965,13 +965,13 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>85.977</v>
+        <v>84.401</v>
       </c>
       <c r="E18" t="n">
-        <v>88.879</v>
+        <v>88.809</v>
       </c>
       <c r="F18" t="n">
-        <v>86.556</v>
+        <v>84.971</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -995,13 +995,13 @@
         <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>47.141</v>
+        <v>48.108</v>
       </c>
       <c r="E19" t="n">
-        <v>49.172</v>
+        <v>51.918</v>
       </c>
       <c r="F19" t="n">
-        <v>47.347</v>
+        <v>49.285</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1025,13 +1025,13 @@
         <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>49.18</v>
+        <v>48.453</v>
       </c>
       <c r="E20" t="n">
-        <v>51.446</v>
+        <v>106.303</v>
       </c>
       <c r="F20" t="n">
-        <v>49.406</v>
+        <v>55.947</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>74.627</v>
+        <v>76.75</v>
       </c>
       <c r="E21" t="n">
-        <v>77.63500000000001</v>
+        <v>82.208</v>
       </c>
       <c r="F21" t="n">
-        <v>75.23999999999999</v>
+        <v>76.94</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1085,13 +1085,13 @@
         <v>30</v>
       </c>
       <c r="D22" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F22" t="n">
         <v>0.721</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.801</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.73</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1115,19 +1115,19 @@
         <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>0.92</v>
+        <v>0.948</v>
       </c>
       <c r="E23" t="n">
-        <v>1.029</v>
+        <v>1.067</v>
       </c>
       <c r="F23" t="n">
-        <v>0.918</v>
+        <v>0.955</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>870</v>
+        <v>810</v>
       </c>
     </row>
     <row r="24">
@@ -1145,13 +1145,13 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>0.043</v>
+        <v>0.041</v>
       </c>
       <c r="E24" t="n">
-        <v>0.051</v>
+        <v>0.067</v>
       </c>
       <c r="F24" t="n">
-        <v>0.043</v>
+        <v>0.045</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1175,13 +1175,13 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>60.015</v>
+        <v>63.392</v>
       </c>
       <c r="E25" t="n">
-        <v>64.70999999999999</v>
+        <v>74.06</v>
       </c>
       <c r="F25" t="n">
-        <v>60.36</v>
+        <v>65.715</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1205,19 +1205,19 @@
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>1.281</v>
+        <v>1.231</v>
       </c>
       <c r="E26" t="n">
-        <v>1.41</v>
+        <v>1.378</v>
       </c>
       <c r="F26" t="n">
-        <v>1.241</v>
+        <v>1.213</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1500</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="27">
@@ -1235,19 +1235,19 @@
         <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>8.894</v>
+        <v>8.912000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>10.178</v>
+        <v>10.026</v>
       </c>
       <c r="F27" t="n">
-        <v>8.871</v>
+        <v>8.694000000000001</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>144300</v>
+        <v>143970</v>
       </c>
     </row>
     <row r="28">
@@ -1265,13 +1265,13 @@
         <v>30</v>
       </c>
       <c r="D28" t="n">
-        <v>43.311</v>
+        <v>40.468</v>
       </c>
       <c r="E28" t="n">
-        <v>53.64</v>
+        <v>44.009</v>
       </c>
       <c r="F28" t="n">
-        <v>45.654</v>
+        <v>41.109</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1295,19 +1295,19 @@
         <v>30</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.734</v>
       </c>
       <c r="E29" t="n">
-        <v>0.783</v>
+        <v>0.828</v>
       </c>
       <c r="F29" t="n">
-        <v>0.705</v>
+        <v>0.732</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>870</v>
+        <v>810</v>
       </c>
     </row>
     <row r="30">
@@ -1325,19 +1325,19 @@
         <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>0.697</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>0.763</v>
+        <v>0.771</v>
       </c>
       <c r="F30" t="n">
-        <v>0.701</v>
+        <v>0.695</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>870</v>
+        <v>810</v>
       </c>
     </row>
     <row r="31">
@@ -1355,19 +1355,19 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>15.533</v>
+        <v>16.267</v>
       </c>
       <c r="E31" t="n">
-        <v>16.306</v>
+        <v>19.628</v>
       </c>
       <c r="F31" t="n">
-        <v>15.627</v>
+        <v>16.757</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>17610</v>
+        <v>17910</v>
       </c>
     </row>
     <row r="32">
@@ -1385,13 +1385,13 @@
         <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>18.531</v>
+        <v>19.247</v>
       </c>
       <c r="E32" t="n">
-        <v>19.559</v>
+        <v>21.457</v>
       </c>
       <c r="F32" t="n">
-        <v>18.658</v>
+        <v>19.629</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1415,13 +1415,13 @@
         <v>30</v>
       </c>
       <c r="D33" t="n">
-        <v>27.686</v>
+        <v>28.238</v>
       </c>
       <c r="E33" t="n">
-        <v>28.372</v>
+        <v>35.266</v>
       </c>
       <c r="F33" t="n">
-        <v>27.771</v>
+        <v>29.191</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1445,13 +1445,13 @@
         <v>30</v>
       </c>
       <c r="D34" t="n">
-        <v>15.356</v>
+        <v>16.479</v>
       </c>
       <c r="E34" t="n">
-        <v>18.775</v>
+        <v>20.364</v>
       </c>
       <c r="F34" t="n">
-        <v>15.804</v>
+        <v>17.082</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1475,13 +1475,13 @@
         <v>30</v>
       </c>
       <c r="D35" t="n">
-        <v>73.91200000000001</v>
+        <v>81.048</v>
       </c>
       <c r="E35" t="n">
-        <v>77.68000000000001</v>
+        <v>90.502</v>
       </c>
       <c r="F35" t="n">
-        <v>72.637</v>
+        <v>82.93899999999999</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1505,13 +1505,13 @@
         <v>30</v>
       </c>
       <c r="D36" t="n">
-        <v>17.046</v>
+        <v>16.569</v>
       </c>
       <c r="E36" t="n">
-        <v>19.331</v>
+        <v>22.189</v>
       </c>
       <c r="F36" t="n">
-        <v>17.477</v>
+        <v>17.517</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1535,13 +1535,13 @@
         <v>30</v>
       </c>
       <c r="D37" t="n">
-        <v>37.262</v>
+        <v>31.326</v>
       </c>
       <c r="E37" t="n">
-        <v>38.546</v>
+        <v>38.804</v>
       </c>
       <c r="F37" t="n">
-        <v>35.956</v>
+        <v>34.322</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1565,13 +1565,13 @@
         <v>30</v>
       </c>
       <c r="D38" t="n">
-        <v>44.058</v>
+        <v>45.307</v>
       </c>
       <c r="E38" t="n">
-        <v>52.371</v>
+        <v>50.893</v>
       </c>
       <c r="F38" t="n">
-        <v>45.735</v>
+        <v>45.429</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1595,13 +1595,13 @@
         <v>30</v>
       </c>
       <c r="D39" t="n">
-        <v>25.878</v>
+        <v>27.173</v>
       </c>
       <c r="E39" t="n">
-        <v>27.079</v>
+        <v>41.237</v>
       </c>
       <c r="F39" t="n">
-        <v>26.04</v>
+        <v>31.125</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1625,13 +1625,13 @@
         <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>29.013</v>
+        <v>29.427</v>
       </c>
       <c r="E40" t="n">
-        <v>30.071</v>
+        <v>32.368</v>
       </c>
       <c r="F40" t="n">
-        <v>29.215</v>
+        <v>29.522</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1655,13 +1655,13 @@
         <v>30</v>
       </c>
       <c r="D41" t="n">
-        <v>31.494</v>
+        <v>33.014</v>
       </c>
       <c r="E41" t="n">
-        <v>32.575</v>
+        <v>36.168</v>
       </c>
       <c r="F41" t="n">
-        <v>31.654</v>
+        <v>32.978</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
